--- a/assets/reference/潜力产品 -原始数据 - 模板.xlsx
+++ b/assets/reference/潜力产品 -原始数据 - 模板.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18350" windowHeight="7000" activeTab="1"/>
+    <workbookView windowWidth="18350" windowHeight="7000"/>
   </bookViews>
   <sheets>
     <sheet name="潜力产品-客户" sheetId="1" r:id="rId1"/>
@@ -21981,7 +21981,8 @@
     <col min="5" max="5" width="11.775" style="2" customWidth="1"/>
     <col min="6" max="6" width="32.1416666666667" style="2" customWidth="1"/>
     <col min="7" max="8" width="23.5666666666667" style="2" customWidth="1"/>
-    <col min="9" max="10" width="8.33333333333333" style="3" customWidth="1"/>
+    <col min="9" max="9" width="15.7166666666667" style="3" customWidth="1"/>
+    <col min="10" max="10" width="8.33333333333333" style="3" customWidth="1"/>
     <col min="11" max="11" width="8.33333333333333" style="4" customWidth="1"/>
     <col min="12" max="13" width="8.33333333333333" style="5" customWidth="1"/>
     <col min="14" max="14" width="8.33333333333333" style="4" customWidth="1"/>
